--- a/stick-world/config/excel/平衡变量.xlsx
+++ b/stick-world/config/excel/平衡变量.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1432,6 +1432,93 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>var_courier_speed</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>command</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>208</v>
+      </c>
+      <c r="D35" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" t="n">
+        <v>600</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>传令兵速度 v1 抽象传播（px/s，=跑步量级）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>var_command_cross_map_distance</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>command</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>100</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>跨图传令 fallback 距离（px，区域距离未命中时）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>var_report_casualty_threshold</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>command</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>MEDIUM 自主档伤亡上报阈值（存活比跌破即报）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
